--- a/Luban/Excel/Buff.xlsx
+++ b/Luban/Excel/Buff.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125AC4E9-9E82-4668-8A55-1C9D6DB674DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Buff" sheetId="1" r:id="rId1"/>
@@ -35,20 +29,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
     <author>think</author>
   </authors>
   <commentList>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J2" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>作者:</t>
         </r>
@@ -56,7 +50,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1,——经过一个时辰</t>
@@ -65,6 +59,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 2,——经过一场战斗
@@ -76,14 +71,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K2" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>作者:</t>
         </r>
@@ -91,7 +86,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1——</t>
@@ -100,13 +95,14 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <charset val="134"/>
           </rPr>
           <t>重复获取累加
 2——重复获取取最高</t>
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="N2" authorId="1">
       <text/>
     </comment>
   </commentList>
@@ -497,8 +493,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,71 +512,402 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -597,26 +930,271 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -625,21 +1203,68 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -889,1485 +1514,1703 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="9" style="5"/>
-    <col min="5" max="5" width="88" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="5"/>
+    <col min="1" max="4" width="9" style="6"/>
+    <col min="5" max="5" width="88" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+    <row r="1" ht="15.6" spans="1:15">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
+    <row r="2" ht="15.6" spans="1:15">
+      <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:15">
+      <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A4" s="5">
+    <row r="4" spans="1:15">
+      <c r="A4" s="6">
         <v>88001</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="5">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8">
         <v>48</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="N4" s="5">
-        <v>1</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A5" s="5">
+      <c r="K4" s="8">
+        <v>2</v>
+      </c>
+      <c r="L4" s="8">
+        <v>1</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8">
+        <v>1</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="6">
         <v>88002</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="5">
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8">
         <v>48</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A6" s="5">
+      <c r="K5" s="8">
+        <v>2</v>
+      </c>
+      <c r="L5" s="8">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8">
+        <v>1</v>
+      </c>
+      <c r="O5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="6">
         <v>88003</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="5">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8">
         <v>48</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="5">
-        <v>2</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="N6" s="5">
-        <v>1</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A7" s="5">
+      <c r="K6" s="8">
+        <v>2</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="6">
         <v>88004</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="5">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8">
         <v>48</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="5">
-        <v>2</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A8" s="5">
+      <c r="K7" s="8">
+        <v>2</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8">
+        <v>1</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="6">
         <v>88005</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="5">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="5">
-        <v>2</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1</v>
-      </c>
-      <c r="N8" s="5">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A9" s="5">
+      <c r="K8" s="8">
+        <v>2</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8">
+        <v>1</v>
+      </c>
+      <c r="O8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="6">
         <v>88006</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="5">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="5">
-        <v>2</v>
-      </c>
-      <c r="L9" s="5">
-        <v>2</v>
-      </c>
-      <c r="N9" s="5">
-        <v>1</v>
-      </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A10" s="5">
+      <c r="K9" s="8">
+        <v>2</v>
+      </c>
+      <c r="L9" s="8">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8">
+        <v>1</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="6">
         <v>88007</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="5">
-        <v>1</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="5">
-        <v>2</v>
-      </c>
-      <c r="L10" s="5">
-        <v>2</v>
-      </c>
-      <c r="N10" s="5">
-        <v>1</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A11" s="5">
+      <c r="K10" s="8">
+        <v>2</v>
+      </c>
+      <c r="L10" s="8">
+        <v>2</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8">
+        <v>1</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="6">
         <v>88008</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="5">
-        <v>1</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="5">
-        <v>2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>2</v>
-      </c>
-      <c r="N11" s="5">
-        <v>1</v>
-      </c>
-      <c r="O11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A12" s="5">
+      <c r="K11" s="8">
+        <v>2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>2</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8">
+        <v>1</v>
+      </c>
+      <c r="O11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="6">
         <v>88009</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="5">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="5">
-        <v>2</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2</v>
-      </c>
-      <c r="N12" s="5">
-        <v>1</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A13" s="5">
+      <c r="K12" s="8">
+        <v>2</v>
+      </c>
+      <c r="L12" s="8">
+        <v>2</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8">
+        <v>1</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="6">
         <v>88010</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="5">
-        <v>1</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="5">
-        <v>2</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2</v>
-      </c>
-      <c r="N13" s="5">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A14" s="5">
+      <c r="K13" s="8">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8">
+        <v>2</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8">
+        <v>1</v>
+      </c>
+      <c r="O13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="6">
         <v>88011</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="5">
-        <v>1</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="5">
-        <v>2</v>
-      </c>
-      <c r="L14" s="5">
-        <v>2</v>
-      </c>
-      <c r="N14" s="5">
-        <v>1</v>
-      </c>
-      <c r="O14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A15" s="5">
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8">
+        <v>2</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8">
+        <v>1</v>
+      </c>
+      <c r="O14" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="6">
         <v>88012</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="5">
-        <v>1</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="5">
-        <v>2</v>
-      </c>
-      <c r="L15" s="5">
-        <v>2</v>
-      </c>
-      <c r="N15" s="5">
-        <v>1</v>
-      </c>
-      <c r="O15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A16" s="5">
+      <c r="K15" s="8">
+        <v>2</v>
+      </c>
+      <c r="L15" s="8">
+        <v>2</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="6">
         <v>88013</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="5">
-        <v>1</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K16" s="5">
-        <v>2</v>
-      </c>
-      <c r="L16" s="5">
-        <v>2</v>
-      </c>
-      <c r="N16" s="5">
-        <v>1</v>
-      </c>
-      <c r="O16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A17" s="5">
+      <c r="K16" s="8">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8">
+        <v>2</v>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8">
+        <v>1</v>
+      </c>
+      <c r="O16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="6">
         <v>88014</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="5">
-        <v>1</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K17" s="5">
-        <v>2</v>
-      </c>
-      <c r="L17" s="5">
-        <v>2</v>
-      </c>
-      <c r="N17" s="5">
-        <v>1</v>
-      </c>
-      <c r="O17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A18" s="5">
+      <c r="K17" s="8">
+        <v>2</v>
+      </c>
+      <c r="L17" s="8">
+        <v>2</v>
+      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="6">
         <v>88015</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="5">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K18" s="5">
-        <v>2</v>
-      </c>
-      <c r="L18" s="5">
-        <v>2</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1</v>
-      </c>
-      <c r="O18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A19" s="5">
+      <c r="K18" s="8">
+        <v>2</v>
+      </c>
+      <c r="L18" s="8">
+        <v>2</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8">
+        <v>1</v>
+      </c>
+      <c r="O18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="6">
         <v>88016</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="5">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="5">
-        <v>2</v>
-      </c>
-      <c r="L19" s="5">
-        <v>2</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1</v>
-      </c>
-      <c r="O19" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" s="5">
+      <c r="K19" s="8">
+        <v>2</v>
+      </c>
+      <c r="L19" s="8">
+        <v>2</v>
+      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="6">
         <v>88017</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="8"/>
+      <c r="C20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="5">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="5">
-        <v>2</v>
-      </c>
-      <c r="L20" s="5">
-        <v>2</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1</v>
-      </c>
-      <c r="O20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A21" s="5">
+      <c r="K20" s="8">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8">
+        <v>2</v>
+      </c>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8">
+        <v>1</v>
+      </c>
+      <c r="O20" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="6">
         <v>88018</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="I21" s="5">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="5">
-        <v>2</v>
-      </c>
-      <c r="L21" s="5">
-        <v>2</v>
-      </c>
-      <c r="N21" s="5">
-        <v>1</v>
-      </c>
-      <c r="O21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A22" s="5">
+      <c r="K21" s="8">
+        <v>2</v>
+      </c>
+      <c r="L21" s="8">
+        <v>2</v>
+      </c>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="6">
         <v>88019</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="8"/>
+      <c r="C22" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I22" s="5">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="5">
-        <v>2</v>
-      </c>
-      <c r="L22" s="5">
-        <v>2</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1</v>
-      </c>
-      <c r="O22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A23" s="5">
+      <c r="K22" s="8">
+        <v>2</v>
+      </c>
+      <c r="L22" s="8">
+        <v>2</v>
+      </c>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8">
+        <v>1</v>
+      </c>
+      <c r="O22" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="6">
         <v>88020</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="8"/>
+      <c r="C23" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I23" s="5">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K23" s="5">
-        <v>2</v>
-      </c>
-      <c r="L23" s="5">
-        <v>2</v>
-      </c>
-      <c r="N23" s="5">
-        <v>1</v>
-      </c>
-      <c r="O23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A24" s="5">
+      <c r="K23" s="8">
+        <v>2</v>
+      </c>
+      <c r="L23" s="8">
+        <v>2</v>
+      </c>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="6">
         <v>88021</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I24" s="5">
-        <v>1</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="5">
-        <v>2</v>
-      </c>
-      <c r="L24" s="5">
-        <v>2</v>
-      </c>
-      <c r="N24" s="5">
-        <v>1</v>
-      </c>
-      <c r="O24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A25" s="5">
+      <c r="K24" s="8">
+        <v>2</v>
+      </c>
+      <c r="L24" s="8">
+        <v>2</v>
+      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8">
+        <v>1</v>
+      </c>
+      <c r="O24" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="6">
         <v>88022</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="5">
-        <v>1</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8">
+        <v>1</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K25" s="5">
-        <v>2</v>
-      </c>
-      <c r="L25" s="5">
-        <v>2</v>
-      </c>
-      <c r="N25" s="5">
-        <v>1</v>
-      </c>
-      <c r="O25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A26" s="5">
+      <c r="K25" s="8">
+        <v>2</v>
+      </c>
+      <c r="L25" s="8">
+        <v>2</v>
+      </c>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="6">
         <v>88023</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="8"/>
+      <c r="C26" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="D26" s="8"/>
+      <c r="E26" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="5">
-        <v>1</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K26" s="5">
-        <v>2</v>
-      </c>
-      <c r="L26" s="5">
-        <v>2</v>
-      </c>
-      <c r="N26" s="5">
-        <v>1</v>
-      </c>
-      <c r="O26" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A27" s="5">
+      <c r="K26" s="8">
+        <v>2</v>
+      </c>
+      <c r="L26" s="8">
+        <v>2</v>
+      </c>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8">
+        <v>1</v>
+      </c>
+      <c r="O26" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="6">
         <v>88024</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="8"/>
+      <c r="C27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I27" s="5">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K27" s="5">
-        <v>2</v>
-      </c>
-      <c r="L27" s="5">
-        <v>2</v>
-      </c>
-      <c r="N27" s="5">
-        <v>1</v>
-      </c>
-      <c r="O27" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A28" s="5">
+      <c r="K27" s="8">
+        <v>2</v>
+      </c>
+      <c r="L27" s="8">
+        <v>2</v>
+      </c>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="6">
         <v>88025</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="8"/>
+      <c r="C28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="D28" s="8"/>
+      <c r="E28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="5">
-        <v>1</v>
-      </c>
-      <c r="J28" s="5" t="s">
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="5">
-        <v>2</v>
-      </c>
-      <c r="L28" s="5">
-        <v>2</v>
-      </c>
-      <c r="N28" s="5">
-        <v>1</v>
-      </c>
-      <c r="O28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A29" s="5">
+      <c r="K28" s="8">
+        <v>2</v>
+      </c>
+      <c r="L28" s="8">
+        <v>2</v>
+      </c>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8">
+        <v>1</v>
+      </c>
+      <c r="O28" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="6">
         <v>88026</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="8"/>
+      <c r="E29" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="I29" s="5">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5" t="s">
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="5">
-        <v>2</v>
-      </c>
-      <c r="L29" s="5">
-        <v>2</v>
-      </c>
-      <c r="N29" s="5">
-        <v>1</v>
-      </c>
-      <c r="O29" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="5">
+      <c r="K29" s="8">
+        <v>2</v>
+      </c>
+      <c r="L29" s="8">
+        <v>2</v>
+      </c>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="6">
         <v>88027</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="D30" s="8"/>
+      <c r="E30" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="I30" s="5">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="s">
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="5">
-        <v>2</v>
-      </c>
-      <c r="L30" s="5">
-        <v>2</v>
-      </c>
-      <c r="N30" s="5">
-        <v>1</v>
-      </c>
-      <c r="O30" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A31" s="5">
+      <c r="K30" s="8">
+        <v>2</v>
+      </c>
+      <c r="L30" s="8">
+        <v>2</v>
+      </c>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8">
+        <v>1</v>
+      </c>
+      <c r="O30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="6">
         <v>88028</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="8"/>
+      <c r="C31" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="D31" s="8"/>
+      <c r="E31" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="5">
-        <v>1</v>
-      </c>
-      <c r="J31" s="5" t="s">
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K31" s="5">
-        <v>2</v>
-      </c>
-      <c r="L31" s="5">
-        <v>2</v>
-      </c>
-      <c r="N31" s="5">
-        <v>1</v>
-      </c>
-      <c r="O31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A32" s="5">
+      <c r="K31" s="8">
+        <v>2</v>
+      </c>
+      <c r="L31" s="8">
+        <v>2</v>
+      </c>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="6">
         <v>88029</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="D32" s="8"/>
+      <c r="E32" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I32" s="5">
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8">
         <v>3</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="5">
-        <v>2</v>
-      </c>
-      <c r="L32" s="5">
-        <v>2</v>
-      </c>
-      <c r="N32" s="5">
-        <v>1</v>
-      </c>
-      <c r="O32" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A33" s="5">
+      <c r="K32" s="8">
+        <v>2</v>
+      </c>
+      <c r="L32" s="8">
+        <v>2</v>
+      </c>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8">
+        <v>1</v>
+      </c>
+      <c r="O32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="6">
         <v>88030</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="8"/>
+      <c r="C33" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="D33" s="8"/>
+      <c r="E33" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="5">
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8">
         <v>3</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K33" s="5">
-        <v>2</v>
-      </c>
-      <c r="L33" s="5">
-        <v>2</v>
-      </c>
-      <c r="N33" s="5">
-        <v>1</v>
-      </c>
-      <c r="O33" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A34" s="5">
+      <c r="K33" s="8">
+        <v>2</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="6">
         <v>88031</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="8"/>
+      <c r="C34" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="I34" s="5">
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8">
         <v>3</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="5">
-        <v>2</v>
-      </c>
-      <c r="L34" s="5">
-        <v>1</v>
-      </c>
-      <c r="N34" s="5">
-        <v>1</v>
-      </c>
-      <c r="O34" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A35" s="5">
+      <c r="K34" s="8">
+        <v>2</v>
+      </c>
+      <c r="L34" s="8">
+        <v>1</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8">
+        <v>1</v>
+      </c>
+      <c r="O34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="6">
         <v>88032</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="8"/>
+      <c r="C35" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="D35" s="8"/>
+      <c r="E35" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="I35" s="5">
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8">
         <v>3</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="5">
-        <v>2</v>
-      </c>
-      <c r="L35" s="5">
-        <v>1</v>
-      </c>
-      <c r="N35" s="5">
-        <v>1</v>
-      </c>
-      <c r="O35" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A36" s="5">
+      <c r="K35" s="8">
+        <v>2</v>
+      </c>
+      <c r="L35" s="8">
+        <v>1</v>
+      </c>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="6">
         <v>88033</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="8"/>
+      <c r="C36" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="D36" s="8"/>
+      <c r="E36" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I36" s="5">
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8">
         <v>3</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="5">
-        <v>2</v>
-      </c>
-      <c r="L36" s="5">
-        <v>1</v>
-      </c>
-      <c r="N36" s="5">
-        <v>1</v>
-      </c>
-      <c r="O36" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A37" s="5">
+      <c r="K36" s="8">
+        <v>2</v>
+      </c>
+      <c r="L36" s="8">
+        <v>1</v>
+      </c>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8">
+        <v>1</v>
+      </c>
+      <c r="O36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="6">
         <v>88034</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="B37" s="8"/>
+      <c r="C37" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="D37" s="8"/>
+      <c r="E37" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="I37" s="5">
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8">
         <v>3</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="5">
-        <v>2</v>
-      </c>
-      <c r="L37" s="5">
-        <v>1</v>
-      </c>
-      <c r="N37" s="5">
-        <v>1</v>
-      </c>
-      <c r="O37" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A38" s="5">
+      <c r="K37" s="8">
+        <v>2</v>
+      </c>
+      <c r="L37" s="8">
+        <v>1</v>
+      </c>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="6">
         <v>88035</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="B38" s="8"/>
+      <c r="C38" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="D38" s="8"/>
+      <c r="E38" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I38" s="5">
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8">
         <v>3</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="5">
-        <v>2</v>
-      </c>
-      <c r="L38" s="5">
-        <v>1</v>
-      </c>
-      <c r="N38" s="5">
-        <v>1</v>
-      </c>
-      <c r="O38" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A39" s="5">
+      <c r="K38" s="8">
+        <v>2</v>
+      </c>
+      <c r="L38" s="8">
+        <v>1</v>
+      </c>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8">
+        <v>1</v>
+      </c>
+      <c r="O38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="6">
         <v>88036</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="B39" s="8"/>
+      <c r="C39" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="D39" s="8"/>
+      <c r="E39" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="I39" s="5">
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8">
         <v>3</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K39" s="5">
-        <v>2</v>
-      </c>
-      <c r="L39" s="5">
-        <v>1</v>
-      </c>
-      <c r="N39" s="5">
-        <v>1</v>
-      </c>
-      <c r="O39" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A40" s="5">
+      <c r="K39" s="8">
+        <v>2</v>
+      </c>
+      <c r="L39" s="8">
+        <v>1</v>
+      </c>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="6">
         <v>88037</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="6">
         <v>99</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K40" s="5">
-        <v>2</v>
-      </c>
-      <c r="L40" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A41" s="5">
+      <c r="K40" s="8">
+        <v>2</v>
+      </c>
+      <c r="L40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="6">
         <v>88038</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I41" s="5">
-        <v>1</v>
-      </c>
-      <c r="J41" s="5" t="s">
+      <c r="I41" s="6">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K41" s="5">
-        <v>2</v>
-      </c>
-      <c r="L41" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A42" s="5">
+      <c r="K41" s="6">
+        <v>2</v>
+      </c>
+      <c r="L41" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="6">
         <v>88039</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="6">
         <v>99</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K42" s="5">
-        <v>2</v>
-      </c>
-      <c r="L42" s="5">
+      <c r="K42" s="6">
+        <v>2</v>
+      </c>
+      <c r="L42" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" s="5">
+    <row r="43" spans="1:12">
+      <c r="A43" s="6">
         <v>88040</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="6">
         <v>99</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K43" s="5">
-        <v>2</v>
-      </c>
-      <c r="L43" s="5">
+      <c r="K43" s="6">
+        <v>2</v>
+      </c>
+      <c r="L43" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A44" s="5">
+    <row r="44" spans="1:12">
+      <c r="A44" s="6">
         <v>88041</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="6">
         <v>99</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K44" s="5">
-        <v>2</v>
-      </c>
-      <c r="L44" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A53" s="5">
+      <c r="K44" s="6">
+        <v>2</v>
+      </c>
+      <c r="L44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="6">
         <v>88500</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="6">
         <v>99</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="J53" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K53" s="5">
-        <v>1</v>
-      </c>
-      <c r="L53" s="5">
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A54" s="5">
+    <row r="54" spans="1:12">
+      <c r="A54" s="6">
         <v>88501</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="6">
         <v>99</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K54" s="5">
-        <v>1</v>
-      </c>
-      <c r="L54" s="5">
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A55" s="5">
+    <row r="55" spans="1:12">
+      <c r="A55" s="6">
         <v>88502</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="6">
         <v>99</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K55" s="5">
-        <v>1</v>
-      </c>
-      <c r="L55" s="5">
+      <c r="K55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A56" s="5">
+    <row r="56" spans="1:12">
+      <c r="A56" s="6">
         <v>88503</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="6">
         <v>99</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K56" s="5">
-        <v>1</v>
-      </c>
-      <c r="L56" s="5">
+      <c r="K56" s="6">
+        <v>1</v>
+      </c>
+      <c r="L56" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A57" s="5">
+    <row r="57" spans="1:12">
+      <c r="A57" s="6">
         <v>88504</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="6">
         <v>99</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K57" s="5">
-        <v>1</v>
-      </c>
-      <c r="L57" s="5">
+      <c r="K57" s="6">
+        <v>1</v>
+      </c>
+      <c r="L57" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A58" s="5">
+    <row r="58" spans="1:12">
+      <c r="A58" s="6">
         <v>88505</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="6">
         <v>99</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K58" s="5">
-        <v>1</v>
-      </c>
-      <c r="L58" s="5">
+      <c r="K58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A59" s="5">
+    <row r="59" spans="1:12">
+      <c r="A59" s="6">
         <v>88506</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="6">
         <v>99</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K59" s="5">
-        <v>1</v>
-      </c>
-      <c r="L59" s="5">
+      <c r="K59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="C60" s="5" t="s">
+    <row r="60" spans="3:5">
+      <c r="C60" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="C61" s="5" t="s">
+    <row r="61" spans="3:10">
+      <c r="C61" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" s="6" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" ht="16.2" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -2378,7 +3221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2389,7 +3232,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2400,7 +3243,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2411,7 +3254,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2422,122 +3265,122 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2545,19 +3388,20 @@
       <c r="C22" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Luban/Excel/Buff.xlsx
+++ b/Luban/Excel/Buff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Buff" sheetId="1" r:id="rId1"/>
@@ -1178,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1194,16 +1194,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1523,1671 +1517,1454 @@
   <dimension ref="A1:O61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="9" style="6"/>
-    <col min="5" max="5" width="88" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="6"/>
+    <col min="1" max="4" width="9" style="5"/>
+    <col min="5" max="5" width="88" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:15">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="15.6" spans="1:15">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="7"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" ht="15.6" spans="1:15">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>88001</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>48</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="8">
-        <v>2</v>
-      </c>
-      <c r="L4" s="8">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8">
-        <v>1</v>
-      </c>
-      <c r="O4" s="8">
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+      <c r="O4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>88002</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <v>48</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="8">
-        <v>2</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8">
-        <v>1</v>
-      </c>
-      <c r="O5" s="8">
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+      <c r="O5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>88003</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8">
+      <c r="I6" s="5">
         <v>48</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="8">
-        <v>2</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8">
-        <v>1</v>
-      </c>
-      <c r="O6" s="8">
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>88004</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <v>48</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="8">
-        <v>2</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8">
-        <v>1</v>
-      </c>
-      <c r="O7" s="8">
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>88005</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="8">
-        <v>2</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8">
-        <v>1</v>
-      </c>
-      <c r="O8" s="8">
+      <c r="K8" s="5">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1</v>
+      </c>
+      <c r="O8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>88006</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="8">
-        <v>2</v>
-      </c>
-      <c r="L9" s="8">
-        <v>2</v>
-      </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8">
-        <v>1</v>
-      </c>
-      <c r="O9" s="8">
+      <c r="K9" s="5">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>88007</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="8">
-        <v>2</v>
-      </c>
-      <c r="L10" s="8">
-        <v>2</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8">
-        <v>1</v>
-      </c>
-      <c r="O10" s="8">
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>88008</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="8">
-        <v>2</v>
-      </c>
-      <c r="L11" s="8">
-        <v>2</v>
-      </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8">
-        <v>1</v>
-      </c>
-      <c r="O11" s="8">
+      <c r="K11" s="5">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>88009</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8">
-        <v>1</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="8">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8">
-        <v>2</v>
-      </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8">
-        <v>1</v>
-      </c>
-      <c r="O12" s="8">
+      <c r="K12" s="5">
+        <v>2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>88010</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8">
-        <v>1</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="8">
-        <v>2</v>
-      </c>
-      <c r="L13" s="8">
-        <v>2</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8">
-        <v>1</v>
-      </c>
-      <c r="O13" s="8">
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+      <c r="O13" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>88011</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8">
-        <v>1</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="8">
-        <v>2</v>
-      </c>
-      <c r="L14" s="8">
-        <v>2</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8">
-        <v>1</v>
-      </c>
-      <c r="O14" s="8">
+      <c r="K14" s="5">
+        <v>2</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
+      <c r="O14" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>88012</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8">
-        <v>1</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="8">
-        <v>2</v>
-      </c>
-      <c r="L15" s="8">
-        <v>2</v>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8">
-        <v>1</v>
-      </c>
-      <c r="O15" s="8">
+      <c r="K15" s="5">
+        <v>2</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+      <c r="O15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>88013</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K16" s="8">
-        <v>2</v>
-      </c>
-      <c r="L16" s="8">
-        <v>2</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8">
-        <v>1</v>
-      </c>
-      <c r="O16" s="8">
+      <c r="K16" s="5">
+        <v>2</v>
+      </c>
+      <c r="L16" s="5">
+        <v>2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>88014</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K17" s="8">
-        <v>2</v>
-      </c>
-      <c r="L17" s="8">
-        <v>2</v>
-      </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8">
-        <v>1</v>
-      </c>
-      <c r="O17" s="8">
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>88015</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K18" s="8">
-        <v>2</v>
-      </c>
-      <c r="L18" s="8">
-        <v>2</v>
-      </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8">
-        <v>1</v>
-      </c>
-      <c r="O18" s="8">
+      <c r="K18" s="5">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5">
+        <v>2</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>88016</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="8">
-        <v>2</v>
-      </c>
-      <c r="L19" s="8">
-        <v>2</v>
-      </c>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8">
-        <v>1</v>
-      </c>
-      <c r="O19" s="8">
+      <c r="K19" s="5">
+        <v>2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>88017</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="8">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8">
-        <v>2</v>
-      </c>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8">
-        <v>1</v>
-      </c>
-      <c r="O20" s="8">
+      <c r="K20" s="5">
+        <v>2</v>
+      </c>
+      <c r="L20" s="5">
+        <v>2</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>88018</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8">
-        <v>1</v>
-      </c>
-      <c r="J21" s="8" t="s">
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="8">
-        <v>2</v>
-      </c>
-      <c r="L21" s="8">
-        <v>2</v>
-      </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8">
-        <v>1</v>
-      </c>
-      <c r="O21" s="8">
+      <c r="K21" s="5">
+        <v>2</v>
+      </c>
+      <c r="L21" s="5">
+        <v>2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>1</v>
+      </c>
+      <c r="O21" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>88019</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8">
-        <v>1</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="8">
-        <v>2</v>
-      </c>
-      <c r="L22" s="8">
-        <v>2</v>
-      </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8">
-        <v>1</v>
-      </c>
-      <c r="O22" s="8">
+      <c r="K22" s="5">
+        <v>2</v>
+      </c>
+      <c r="L22" s="5">
+        <v>2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>88020</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8">
-        <v>1</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="I23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K23" s="8">
-        <v>2</v>
-      </c>
-      <c r="L23" s="8">
-        <v>2</v>
-      </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8">
-        <v>1</v>
-      </c>
-      <c r="O23" s="8">
+      <c r="K23" s="5">
+        <v>2</v>
+      </c>
+      <c r="L23" s="5">
+        <v>2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1</v>
+      </c>
+      <c r="O23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>88021</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8">
-        <v>1</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="I24" s="5">
+        <v>1</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="8">
-        <v>2</v>
-      </c>
-      <c r="L24" s="8">
-        <v>2</v>
-      </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8">
-        <v>1</v>
-      </c>
-      <c r="O24" s="8">
+      <c r="K24" s="5">
+        <v>2</v>
+      </c>
+      <c r="L24" s="5">
+        <v>2</v>
+      </c>
+      <c r="N24" s="5">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>88022</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="5">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K25" s="8">
-        <v>2</v>
-      </c>
-      <c r="L25" s="8">
-        <v>2</v>
-      </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8">
-        <v>1</v>
-      </c>
-      <c r="O25" s="8">
+      <c r="K25" s="5">
+        <v>2</v>
+      </c>
+      <c r="L25" s="5">
+        <v>2</v>
+      </c>
+      <c r="N25" s="5">
+        <v>1</v>
+      </c>
+      <c r="O25" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>88023</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8">
-        <v>1</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="I26" s="5">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K26" s="8">
-        <v>2</v>
-      </c>
-      <c r="L26" s="8">
-        <v>2</v>
-      </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8">
-        <v>1</v>
-      </c>
-      <c r="O26" s="8">
+      <c r="K26" s="5">
+        <v>2</v>
+      </c>
+      <c r="L26" s="5">
+        <v>2</v>
+      </c>
+      <c r="N26" s="5">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>88024</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8">
-        <v>1</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="I27" s="5">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K27" s="8">
-        <v>2</v>
-      </c>
-      <c r="L27" s="8">
-        <v>2</v>
-      </c>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8">
-        <v>1</v>
-      </c>
-      <c r="O27" s="8">
+      <c r="K27" s="5">
+        <v>2</v>
+      </c>
+      <c r="L27" s="5">
+        <v>2</v>
+      </c>
+      <c r="N27" s="5">
+        <v>1</v>
+      </c>
+      <c r="O27" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>88025</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="I28" s="5">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="8">
-        <v>2</v>
-      </c>
-      <c r="L28" s="8">
-        <v>2</v>
-      </c>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8">
-        <v>1</v>
-      </c>
-      <c r="O28" s="8">
+      <c r="K28" s="5">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5">
+        <v>2</v>
+      </c>
+      <c r="N28" s="5">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>88026</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8">
-        <v>1</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="8">
-        <v>2</v>
-      </c>
-      <c r="L29" s="8">
-        <v>2</v>
-      </c>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8">
-        <v>1</v>
-      </c>
-      <c r="O29" s="8">
+      <c r="K29" s="5">
+        <v>2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>2</v>
+      </c>
+      <c r="N29" s="5">
+        <v>1</v>
+      </c>
+      <c r="O29" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>88027</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="5">
+        <v>1</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="8">
-        <v>2</v>
-      </c>
-      <c r="L30" s="8">
-        <v>2</v>
-      </c>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8">
-        <v>1</v>
-      </c>
-      <c r="O30" s="8">
+      <c r="K30" s="5">
+        <v>2</v>
+      </c>
+      <c r="L30" s="5">
+        <v>2</v>
+      </c>
+      <c r="N30" s="5">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>88028</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="I31" s="5">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K31" s="8">
-        <v>2</v>
-      </c>
-      <c r="L31" s="8">
-        <v>2</v>
-      </c>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8">
-        <v>1</v>
-      </c>
-      <c r="O31" s="8">
+      <c r="K31" s="5">
+        <v>2</v>
+      </c>
+      <c r="L31" s="5">
+        <v>2</v>
+      </c>
+      <c r="N31" s="5">
+        <v>1</v>
+      </c>
+      <c r="O31" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>88029</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <v>3</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="8">
-        <v>2</v>
-      </c>
-      <c r="L32" s="8">
-        <v>2</v>
-      </c>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8">
-        <v>1</v>
-      </c>
-      <c r="O32" s="8">
+      <c r="K32" s="5">
+        <v>2</v>
+      </c>
+      <c r="L32" s="5">
+        <v>2</v>
+      </c>
+      <c r="N32" s="5">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>88030</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8">
+      <c r="I33" s="5">
         <v>3</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K33" s="8">
-        <v>2</v>
-      </c>
-      <c r="L33" s="8">
-        <v>2</v>
-      </c>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8">
-        <v>1</v>
-      </c>
-      <c r="O33" s="8">
+      <c r="K33" s="5">
+        <v>2</v>
+      </c>
+      <c r="L33" s="5">
+        <v>2</v>
+      </c>
+      <c r="N33" s="5">
+        <v>1</v>
+      </c>
+      <c r="O33" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="6">
+      <c r="A34" s="5">
         <v>88031</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <v>3</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="8">
-        <v>2</v>
-      </c>
-      <c r="L34" s="8">
-        <v>1</v>
-      </c>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8">
-        <v>1</v>
-      </c>
-      <c r="O34" s="8">
+      <c r="K34" s="5">
+        <v>2</v>
+      </c>
+      <c r="L34" s="5">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>88032</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <v>3</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="8">
-        <v>2</v>
-      </c>
-      <c r="L35" s="8">
-        <v>1</v>
-      </c>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8">
-        <v>1</v>
-      </c>
-      <c r="O35" s="8">
+      <c r="K35" s="5">
+        <v>2</v>
+      </c>
+      <c r="L35" s="5">
+        <v>1</v>
+      </c>
+      <c r="N35" s="5">
+        <v>1</v>
+      </c>
+      <c r="O35" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>88033</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8">
+      <c r="I36" s="5">
         <v>3</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="J36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="8">
-        <v>2</v>
-      </c>
-      <c r="L36" s="8">
-        <v>1</v>
-      </c>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8">
-        <v>1</v>
-      </c>
-      <c r="O36" s="8">
+      <c r="K36" s="5">
+        <v>2</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1</v>
+      </c>
+      <c r="N36" s="5">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>88034</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8">
+      <c r="I37" s="5">
         <v>3</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="8">
-        <v>2</v>
-      </c>
-      <c r="L37" s="8">
-        <v>1</v>
-      </c>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8">
-        <v>1</v>
-      </c>
-      <c r="O37" s="8">
+      <c r="K37" s="5">
+        <v>2</v>
+      </c>
+      <c r="L37" s="5">
+        <v>1</v>
+      </c>
+      <c r="N37" s="5">
+        <v>1</v>
+      </c>
+      <c r="O37" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>88035</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8">
+      <c r="I38" s="5">
         <v>3</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="8">
-        <v>2</v>
-      </c>
-      <c r="L38" s="8">
-        <v>1</v>
-      </c>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8">
-        <v>1</v>
-      </c>
-      <c r="O38" s="8">
+      <c r="K38" s="5">
+        <v>2</v>
+      </c>
+      <c r="L38" s="5">
+        <v>1</v>
+      </c>
+      <c r="N38" s="5">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>88036</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8">
+      <c r="I39" s="5">
         <v>3</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K39" s="8">
-        <v>2</v>
-      </c>
-      <c r="L39" s="8">
-        <v>1</v>
-      </c>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8">
-        <v>1</v>
-      </c>
-      <c r="O39" s="8">
+      <c r="K39" s="5">
+        <v>2</v>
+      </c>
+      <c r="L39" s="5">
+        <v>1</v>
+      </c>
+      <c r="N39" s="5">
+        <v>1</v>
+      </c>
+      <c r="O39" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="6">
+      <c r="A40" s="5">
         <v>88037</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>99</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K40" s="8">
-        <v>2</v>
-      </c>
-      <c r="L40" s="6">
+      <c r="K40" s="5">
+        <v>2</v>
+      </c>
+      <c r="L40" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="6">
+      <c r="A41" s="5">
         <v>88038</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="I41" s="6">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8" t="s">
+      <c r="I41" s="5">
+        <v>1</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K41" s="6">
-        <v>2</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="K41" s="5">
+        <v>2</v>
+      </c>
+      <c r="L41" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="6">
+      <c r="A42" s="5">
         <v>88039</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>99</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="J42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K42" s="6">
-        <v>2</v>
-      </c>
-      <c r="L42" s="6">
+      <c r="K42" s="5">
+        <v>2</v>
+      </c>
+      <c r="L42" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="6">
+      <c r="A43" s="5">
         <v>88040</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="5">
         <v>99</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="J43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K43" s="6">
-        <v>2</v>
-      </c>
-      <c r="L43" s="6">
+      <c r="K43" s="5">
+        <v>2</v>
+      </c>
+      <c r="L43" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>88041</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="5">
         <v>99</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="J44" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K44" s="6">
-        <v>2</v>
-      </c>
-      <c r="L44" s="6">
+      <c r="K44" s="5">
+        <v>2</v>
+      </c>
+      <c r="L44" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="6">
+      <c r="A53" s="5">
         <v>88500</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I53" s="5">
         <v>99</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6">
+      <c r="K53" s="5">
+        <v>1</v>
+      </c>
+      <c r="L53" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="6">
+      <c r="A54" s="5">
         <v>88501</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="5">
         <v>99</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6">
+      <c r="K54" s="5">
+        <v>1</v>
+      </c>
+      <c r="L54" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>88502</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="5">
         <v>99</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K55" s="6">
-        <v>1</v>
-      </c>
-      <c r="L55" s="6">
+      <c r="K55" s="5">
+        <v>1</v>
+      </c>
+      <c r="L55" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="6">
+      <c r="A56" s="5">
         <v>88503</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I56" s="6">
+      <c r="I56" s="5">
         <v>99</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K56" s="6">
-        <v>1</v>
-      </c>
-      <c r="L56" s="6">
+      <c r="K56" s="5">
+        <v>1</v>
+      </c>
+      <c r="L56" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="6">
+      <c r="A57" s="5">
         <v>88504</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I57" s="5">
         <v>99</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K57" s="6">
-        <v>1</v>
-      </c>
-      <c r="L57" s="6">
+      <c r="K57" s="5">
+        <v>1</v>
+      </c>
+      <c r="L57" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="6">
+      <c r="A58" s="5">
         <v>88505</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="5">
         <v>99</v>
       </c>
-      <c r="J58" s="6" t="s">
+      <c r="J58" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K58" s="6">
-        <v>1</v>
-      </c>
-      <c r="L58" s="6">
+      <c r="K58" s="5">
+        <v>1</v>
+      </c>
+      <c r="L58" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="6">
+      <c r="A59" s="5">
         <v>88506</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I59" s="5">
         <v>99</v>
       </c>
-      <c r="J59" s="6" t="s">
+      <c r="J59" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K59" s="6">
-        <v>1</v>
-      </c>
-      <c r="L59" s="6">
+      <c r="K59" s="5">
+        <v>1</v>
+      </c>
+      <c r="L59" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="61" spans="3:10">
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="J61" s="6" t="s">
+      <c r="J61" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3278,7 +3055,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="1" t="s">
         <v>125</v>
       </c>
     </row>
